--- a/gstdatabase/GSTR-3B-2019-2020.xlsx
+++ b/gstdatabase/GSTR-3B-2019-2020.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C146DE02-F707-4A3B-9476-DE706191E4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1C015F-2FB3-4F3E-9516-C4E2998D6A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>STATE WISE RETURN PERIOD WISE GSTR-3B FILING SUMMARY</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1452,11 +1452,11 @@
         <v>279876</v>
       </c>
       <c r="F12" s="3">
-        <v>279918</v>
+        <v>279919</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" si="0"/>
-        <v>0.91750222067803611</v>
+        <v>0.9175054984315949</v>
       </c>
       <c r="H12" s="10">
         <v>307464</v>
@@ -1466,14 +1466,14 @@
       </c>
       <c r="J12" s="11">
         <f t="shared" si="1"/>
-        <v>47829</v>
+        <v>47830</v>
       </c>
       <c r="K12" s="3">
-        <v>281537</v>
+        <v>281538</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" si="2"/>
-        <v>0.91567468061301482</v>
+        <v>0.91567793302630551</v>
       </c>
       <c r="M12" s="10">
         <v>308875</v>
@@ -1483,14 +1483,14 @@
       </c>
       <c r="O12" s="11">
         <f t="shared" si="3"/>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="P12" s="3">
-        <v>282419</v>
+        <v>282420</v>
       </c>
       <c r="Q12" s="12">
         <f t="shared" si="4"/>
-        <v>0.9143472278429785</v>
+        <v>0.91435046539862408</v>
       </c>
       <c r="R12" s="10">
         <v>310093</v>
@@ -1500,14 +1500,14 @@
       </c>
       <c r="T12" s="11">
         <f t="shared" si="5"/>
-        <v>36697</v>
+        <v>36698</v>
       </c>
       <c r="U12" s="3">
-        <v>283783</v>
+        <v>283784</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="6"/>
-        <v>0.91515448591229087</v>
+        <v>0.91515771075129071</v>
       </c>
       <c r="W12" s="10">
         <v>310860</v>
@@ -1517,14 +1517,14 @@
       </c>
       <c r="Y12" s="11">
         <f t="shared" si="7"/>
-        <v>52168</v>
+        <v>52169</v>
       </c>
       <c r="Z12" s="3">
-        <v>284819</v>
+        <v>284820</v>
       </c>
       <c r="AA12" s="12">
         <f t="shared" si="8"/>
-        <v>0.91622917068776943</v>
+        <v>0.91623238756996717</v>
       </c>
       <c r="AB12" s="10">
         <v>311089</v>
@@ -1534,14 +1534,14 @@
       </c>
       <c r="AD12" s="11">
         <f t="shared" si="9"/>
-        <v>78534</v>
+        <v>78535</v>
       </c>
       <c r="AE12" s="3">
-        <v>286193</v>
+        <v>286194</v>
       </c>
       <c r="AF12" s="12">
         <f t="shared" si="10"/>
-        <v>0.91997145511413136</v>
+        <v>0.91997466962830576</v>
       </c>
       <c r="AG12" s="10">
         <v>309832</v>
@@ -1551,14 +1551,14 @@
       </c>
       <c r="AI12" s="11">
         <f t="shared" si="11"/>
-        <v>64629</v>
+        <v>64630</v>
       </c>
       <c r="AJ12" s="3">
-        <v>287456</v>
+        <v>287457</v>
       </c>
       <c r="AK12" s="12">
         <f t="shared" si="12"/>
-        <v>0.92778021637532593</v>
+        <v>0.92778344393090451</v>
       </c>
       <c r="AL12" s="10">
         <v>309106</v>
@@ -1568,14 +1568,14 @@
       </c>
       <c r="AN12" s="11">
         <f t="shared" si="13"/>
-        <v>31056</v>
+        <v>31057</v>
       </c>
       <c r="AO12" s="3">
-        <v>288427</v>
+        <v>288428</v>
       </c>
       <c r="AP12" s="12">
         <f t="shared" si="14"/>
-        <v>0.93310061920506238</v>
+        <v>0.93310385434122922</v>
       </c>
       <c r="AQ12" s="10">
         <v>308579</v>
@@ -1585,14 +1585,14 @@
       </c>
       <c r="AS12" s="11">
         <f t="shared" si="15"/>
-        <v>67338</v>
+        <v>67339</v>
       </c>
       <c r="AT12" s="3">
-        <v>290110</v>
+        <v>290111</v>
       </c>
       <c r="AU12" s="12">
         <f t="shared" si="16"/>
-        <v>0.94014822784440932</v>
+        <v>0.94015146850563391</v>
       </c>
       <c r="AV12" s="10">
         <v>309304</v>
@@ -1602,14 +1602,14 @@
       </c>
       <c r="AX12" s="11">
         <f t="shared" si="17"/>
-        <v>32677</v>
+        <v>32678</v>
       </c>
       <c r="AY12" s="3">
-        <v>291681</v>
+        <v>291682</v>
       </c>
       <c r="AZ12" s="12">
         <f t="shared" si="18"/>
-        <v>0.94302369190181823</v>
+        <v>0.94302692496702278</v>
       </c>
       <c r="BA12" s="10">
         <v>310694</v>
@@ -1619,14 +1619,14 @@
       </c>
       <c r="BC12" s="11">
         <f t="shared" si="19"/>
-        <v>59879</v>
+        <v>59880</v>
       </c>
       <c r="BD12" s="3">
-        <v>293022</v>
+        <v>293023</v>
       </c>
       <c r="BE12" s="12">
         <f t="shared" si="20"/>
-        <v>0.94312088421404983</v>
+        <v>0.94312410281498837</v>
       </c>
       <c r="BF12" s="10">
         <v>312194</v>
@@ -1636,14 +1636,14 @@
       </c>
       <c r="BH12" s="11">
         <f t="shared" si="21"/>
-        <v>281200</v>
+        <v>281201</v>
       </c>
       <c r="BI12" s="3">
-        <v>294508</v>
+        <v>294509</v>
       </c>
       <c r="BJ12" s="12">
         <f t="shared" si="22"/>
-        <v>0.94334932766164625</v>
+        <v>0.94335253079815751</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -2085,11 +2085,11 @@
         <v>373644</v>
       </c>
       <c r="F15" s="3">
-        <v>373726</v>
+        <v>373727</v>
       </c>
       <c r="G15" s="12">
         <f t="shared" si="0"/>
-        <v>0.88369684473365617</v>
+        <v>0.8836992092917676</v>
       </c>
       <c r="H15" s="10">
         <v>423730</v>
@@ -2099,14 +2099,14 @@
       </c>
       <c r="J15" s="11">
         <f t="shared" si="1"/>
-        <v>89252</v>
+        <v>89253</v>
       </c>
       <c r="K15" s="3">
-        <v>375879</v>
+        <v>375880</v>
       </c>
       <c r="L15" s="12">
         <f t="shared" si="2"/>
-        <v>0.88707195619852264</v>
+        <v>0.88707431619191468</v>
       </c>
       <c r="M15" s="10">
         <v>423764</v>
@@ -2116,14 +2116,14 @@
       </c>
       <c r="O15" s="11">
         <f t="shared" si="3"/>
-        <v>86699</v>
+        <v>86700</v>
       </c>
       <c r="P15" s="3">
-        <v>376579</v>
+        <v>376580</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="4"/>
-        <v>0.88865264628425256</v>
+        <v>0.8886550060882944</v>
       </c>
       <c r="R15" s="10">
         <v>424544</v>
@@ -2133,14 +2133,14 @@
       </c>
       <c r="T15" s="11">
         <f t="shared" si="5"/>
-        <v>70755</v>
+        <v>70756</v>
       </c>
       <c r="U15" s="3">
-        <v>378389</v>
+        <v>378390</v>
       </c>
       <c r="V15" s="12">
         <f t="shared" si="6"/>
-        <v>0.89128335343333087</v>
+        <v>0.89128570890178638</v>
       </c>
       <c r="W15" s="10">
         <v>425499</v>
@@ -2150,14 +2150,14 @@
       </c>
       <c r="Y15" s="11">
         <f t="shared" si="7"/>
-        <v>93076</v>
+        <v>93077</v>
       </c>
       <c r="Z15" s="3">
-        <v>380148</v>
+        <v>380149</v>
       </c>
       <c r="AA15" s="12">
         <f t="shared" si="8"/>
-        <v>0.89341690579766342</v>
+        <v>0.89341925597945004</v>
       </c>
       <c r="AB15" s="10">
         <v>423483</v>
@@ -2167,14 +2167,14 @@
       </c>
       <c r="AD15" s="11">
         <f t="shared" si="9"/>
-        <v>125545</v>
+        <v>125546</v>
       </c>
       <c r="AE15" s="3">
-        <v>382802</v>
+        <v>382803</v>
       </c>
       <c r="AF15" s="12">
         <f t="shared" si="10"/>
-        <v>0.90393711199741189</v>
+        <v>0.90393947336728986</v>
       </c>
       <c r="AG15" s="10">
         <v>424856</v>
@@ -2184,14 +2184,14 @@
       </c>
       <c r="AI15" s="11">
         <f t="shared" si="11"/>
-        <v>106882</v>
+        <v>106883</v>
       </c>
       <c r="AJ15" s="3">
-        <v>384875</v>
+        <v>384876</v>
       </c>
       <c r="AK15" s="12">
         <f t="shared" si="12"/>
-        <v>0.90589517389421359</v>
+        <v>0.90589752763289211</v>
       </c>
       <c r="AL15" s="10">
         <v>424839</v>
@@ -2201,14 +2201,14 @@
       </c>
       <c r="AN15" s="11">
         <f t="shared" si="13"/>
-        <v>60994</v>
+        <v>60995</v>
       </c>
       <c r="AO15" s="3">
-        <v>387670</v>
+        <v>387671</v>
       </c>
       <c r="AP15" s="12">
         <f t="shared" si="14"/>
-        <v>0.91251038628751124</v>
+        <v>0.91251274012037498</v>
       </c>
       <c r="AQ15" s="10">
         <v>424443</v>
@@ -2218,14 +2218,14 @@
       </c>
       <c r="AS15" s="11">
         <f t="shared" si="15"/>
-        <v>112477</v>
+        <v>112478</v>
       </c>
       <c r="AT15" s="3">
-        <v>390042</v>
+        <v>390043</v>
       </c>
       <c r="AU15" s="12">
         <f t="shared" si="16"/>
-        <v>0.91895024773644518</v>
+        <v>0.91895260376540544</v>
       </c>
       <c r="AV15" s="10">
         <v>424329</v>
@@ -2235,14 +2235,14 @@
       </c>
       <c r="AX15" s="11">
         <f t="shared" si="17"/>
-        <v>63094</v>
+        <v>63095</v>
       </c>
       <c r="AY15" s="3">
-        <v>391319</v>
+        <v>391320</v>
       </c>
       <c r="AZ15" s="12">
         <f t="shared" si="18"/>
-        <v>0.922206589698088</v>
+        <v>0.92220894636001782</v>
       </c>
       <c r="BA15" s="10">
         <v>421659</v>
@@ -2252,14 +2252,14 @@
       </c>
       <c r="BC15" s="11">
         <f t="shared" si="19"/>
-        <v>93166</v>
+        <v>93167</v>
       </c>
       <c r="BD15" s="3">
-        <v>393775</v>
+        <v>393776</v>
       </c>
       <c r="BE15" s="12">
         <f t="shared" si="20"/>
-        <v>0.93387073440860979</v>
+        <v>0.93387310599323148</v>
       </c>
       <c r="BF15" s="10">
         <v>423351</v>
@@ -2269,14 +2269,14 @@
       </c>
       <c r="BH15" s="11">
         <f t="shared" si="21"/>
-        <v>367413</v>
+        <v>367414</v>
       </c>
       <c r="BI15" s="3">
-        <v>394150</v>
+        <v>394151</v>
       </c>
       <c r="BJ15" s="12">
         <f t="shared" si="22"/>
-        <v>0.93102413836272979</v>
+        <v>0.93102650046887803</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2507,11 +2507,11 @@
         <v>487170</v>
       </c>
       <c r="F17" s="3">
-        <v>487420</v>
+        <v>487421</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="0"/>
-        <v>0.88028347071019386</v>
+        <v>0.88028527671624757</v>
       </c>
       <c r="H17" s="10">
         <v>557836</v>
@@ -2521,14 +2521,14 @@
       </c>
       <c r="J17" s="11">
         <f t="shared" si="1"/>
-        <v>119062</v>
+        <v>119063</v>
       </c>
       <c r="K17" s="3">
-        <v>491129</v>
+        <v>491130</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="2"/>
-        <v>0.88041825912992344</v>
+        <v>0.88042005177148841</v>
       </c>
       <c r="M17" s="10">
         <v>560439</v>
@@ -2538,14 +2538,14 @@
       </c>
       <c r="O17" s="11">
         <f t="shared" si="3"/>
-        <v>114185</v>
+        <v>114186</v>
       </c>
       <c r="P17" s="3">
-        <v>494271</v>
+        <v>494272</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="4"/>
-        <v>0.88193541134717601</v>
+        <v>0.88193719566268591</v>
       </c>
       <c r="R17" s="10">
         <v>561513</v>
@@ -2555,14 +2555,14 @@
       </c>
       <c r="T17" s="11">
         <f t="shared" si="5"/>
-        <v>96206</v>
+        <v>96207</v>
       </c>
       <c r="U17" s="3">
-        <v>498347</v>
+        <v>498348</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="6"/>
-        <v>0.88750750205249029</v>
+        <v>0.88750928295515863</v>
       </c>
       <c r="W17" s="10">
         <v>560642</v>
@@ -2572,14 +2572,14 @@
       </c>
       <c r="Y17" s="11">
         <f t="shared" si="7"/>
-        <v>126340</v>
+        <v>126341</v>
       </c>
       <c r="Z17" s="3">
-        <v>500738</v>
+        <v>500739</v>
       </c>
       <c r="AA17" s="12">
         <f t="shared" si="8"/>
-        <v>0.89315106609922201</v>
+        <v>0.89315284976865805</v>
       </c>
       <c r="AB17" s="10">
         <v>559918</v>
@@ -2589,14 +2589,14 @@
       </c>
       <c r="AD17" s="11">
         <f t="shared" si="9"/>
-        <v>167231</v>
+        <v>167232</v>
       </c>
       <c r="AE17" s="3">
-        <v>504385</v>
+        <v>504386</v>
       </c>
       <c r="AF17" s="12">
         <f t="shared" si="10"/>
-        <v>0.90081940569869157</v>
+        <v>0.90082119167449515</v>
       </c>
       <c r="AG17" s="10">
         <v>561583</v>
@@ -2606,14 +2606,14 @@
       </c>
       <c r="AI17" s="11">
         <f t="shared" si="11"/>
-        <v>143633</v>
+        <v>143634</v>
       </c>
       <c r="AJ17" s="3">
-        <v>508327</v>
+        <v>508328</v>
       </c>
       <c r="AK17" s="12">
         <f t="shared" si="12"/>
-        <v>0.90516806954626472</v>
+        <v>0.90516985022694774</v>
       </c>
       <c r="AL17" s="10">
         <v>559753</v>
@@ -2623,14 +2623,14 @@
       </c>
       <c r="AN17" s="11">
         <f t="shared" si="13"/>
-        <v>81142</v>
+        <v>81143</v>
       </c>
       <c r="AO17" s="3">
-        <v>511821</v>
+        <v>511822</v>
       </c>
       <c r="AP17" s="12">
         <f t="shared" si="14"/>
-        <v>0.91436937363444237</v>
+        <v>0.91437116013670316</v>
       </c>
       <c r="AQ17" s="10">
         <v>541872</v>
@@ -2640,14 +2640,14 @@
       </c>
       <c r="AS17" s="11">
         <f t="shared" si="15"/>
-        <v>151532</v>
+        <v>151533</v>
       </c>
       <c r="AT17" s="3">
-        <v>515485</v>
+        <v>515486</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="16"/>
-        <v>0.95130399799214571</v>
+        <v>0.95130584344642277</v>
       </c>
       <c r="AV17" s="10">
         <v>543495</v>
@@ -2749,14 +2749,14 @@
       </c>
       <c r="O18" s="11">
         <f t="shared" si="3"/>
-        <v>221701</v>
+        <v>221702</v>
       </c>
       <c r="P18" s="3">
-        <v>991281</v>
+        <v>991282</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="4"/>
-        <v>0.88611112849259888</v>
+        <v>0.88611202239768583</v>
       </c>
       <c r="R18" s="10">
         <v>1127309</v>
@@ -2766,14 +2766,14 @@
       </c>
       <c r="T18" s="11">
         <f t="shared" si="5"/>
-        <v>178384</v>
+        <v>178385</v>
       </c>
       <c r="U18" s="3">
-        <v>1000098</v>
+        <v>1000099</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="6"/>
-        <v>0.88715516331369659</v>
+        <v>0.88715605038192724</v>
       </c>
       <c r="W18" s="10">
         <v>1128388</v>
@@ -2783,14 +2783,14 @@
       </c>
       <c r="Y18" s="11">
         <f t="shared" si="7"/>
-        <v>244988</v>
+        <v>244989</v>
       </c>
       <c r="Z18" s="3">
-        <v>1007722</v>
+        <v>1007723</v>
       </c>
       <c r="AA18" s="12">
         <f t="shared" si="8"/>
-        <v>0.89306337890867327</v>
+        <v>0.89306426512866144</v>
       </c>
       <c r="AB18" s="10">
         <v>1126122</v>
@@ -2800,14 +2800,14 @@
       </c>
       <c r="AD18" s="11">
         <f t="shared" si="9"/>
-        <v>308058</v>
+        <v>308059</v>
       </c>
       <c r="AE18" s="3">
-        <v>1016959</v>
+        <v>1016960</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="10"/>
-        <v>0.90306290082246865</v>
+        <v>0.90306378882572225</v>
       </c>
       <c r="AG18" s="10">
         <v>1126652</v>
@@ -2817,14 +2817,14 @@
       </c>
       <c r="AI18" s="11">
         <f t="shared" si="11"/>
-        <v>271501</v>
+        <v>271503</v>
       </c>
       <c r="AJ18" s="3">
-        <v>1026209</v>
+        <v>1026211</v>
       </c>
       <c r="AK18" s="12">
         <f t="shared" si="12"/>
-        <v>0.91084824772866868</v>
+        <v>0.9108500228997064</v>
       </c>
       <c r="AL18" s="10">
         <v>1124411</v>
@@ -2834,14 +2834,14 @@
       </c>
       <c r="AN18" s="11">
         <f t="shared" si="13"/>
-        <v>195021</v>
+        <v>195024</v>
       </c>
       <c r="AO18" s="3">
-        <v>1036129</v>
+        <v>1036132</v>
       </c>
       <c r="AP18" s="12">
         <f t="shared" si="14"/>
-        <v>0.92148600467266861</v>
+        <v>0.92148867273621482</v>
       </c>
       <c r="AQ18" s="10">
         <v>1127354</v>
@@ -2851,14 +2851,14 @@
       </c>
       <c r="AS18" s="11">
         <f t="shared" si="15"/>
-        <v>311783</v>
+        <v>311786</v>
       </c>
       <c r="AT18" s="3">
-        <v>1046796</v>
+        <v>1046799</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="16"/>
-        <v>0.92854240992625214</v>
+        <v>0.92854507102471806</v>
       </c>
       <c r="AV18" s="10">
         <v>1133999</v>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="AX18" s="11">
         <f t="shared" si="17"/>
-        <v>165991</v>
+        <v>165993</v>
       </c>
       <c r="AY18" s="3">
-        <v>1059069</v>
+        <v>1059071</v>
       </c>
       <c r="AZ18" s="12">
         <f t="shared" si="18"/>
-        <v>0.93392410398950965</v>
+        <v>0.93392586765949526</v>
       </c>
       <c r="BA18" s="10">
         <v>1144874</v>
@@ -2885,14 +2885,14 @@
       </c>
       <c r="BC18" s="11">
         <f t="shared" si="19"/>
-        <v>239380</v>
+        <v>239381</v>
       </c>
       <c r="BD18" s="3">
-        <v>1070499</v>
+        <v>1070500</v>
       </c>
       <c r="BE18" s="12">
         <f t="shared" si="20"/>
-        <v>0.93503651930256082</v>
+        <v>0.93503739276112485</v>
       </c>
       <c r="BF18" s="10">
         <v>1155076</v>
@@ -3113,14 +3113,14 @@
       </c>
       <c r="BH19" s="11">
         <f t="shared" si="21"/>
-        <v>273792</v>
+        <v>273793</v>
       </c>
       <c r="BI19" s="3">
-        <v>296540</v>
+        <v>296541</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="22"/>
-        <v>0.925706829327681</v>
+        <v>0.92570995102063747</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3984,11 +3984,11 @@
         <v>4208</v>
       </c>
       <c r="F24" s="3">
-        <v>4216</v>
+        <v>4217</v>
       </c>
       <c r="G24" s="12">
         <f t="shared" si="0"/>
-        <v>0.79502168583820476</v>
+        <v>0.79521025834433334</v>
       </c>
       <c r="H24" s="10">
         <v>5386</v>
@@ -3998,14 +3998,14 @@
       </c>
       <c r="J24" s="11">
         <f t="shared" si="1"/>
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="K24" s="3">
-        <v>4280</v>
+        <v>4281</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="2"/>
-        <v>0.79465280356479762</v>
+        <v>0.7948384701076866</v>
       </c>
       <c r="M24" s="10">
         <v>5454</v>
@@ -4015,14 +4015,14 @@
       </c>
       <c r="O24" s="11">
         <f t="shared" si="3"/>
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="P24" s="3">
-        <v>4335</v>
+        <v>4336</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="4"/>
-        <v>0.79482948294829481</v>
+        <v>0.79501283461679506</v>
       </c>
       <c r="R24" s="10">
         <v>5617</v>
@@ -4032,14 +4032,14 @@
       </c>
       <c r="T24" s="11">
         <f t="shared" si="5"/>
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="U24" s="3">
-        <v>4441</v>
+        <v>4442</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="6"/>
-        <v>0.79063557058928258</v>
+        <v>0.79081360156667257</v>
       </c>
       <c r="W24" s="10">
         <v>5716</v>
@@ -4049,14 +4049,14 @@
       </c>
       <c r="Y24" s="11">
         <f t="shared" si="7"/>
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="Z24" s="3">
-        <v>4491</v>
+        <v>4492</v>
       </c>
       <c r="AA24" s="12">
         <f t="shared" si="8"/>
-        <v>0.7856892932120364</v>
+        <v>0.78586424072778172</v>
       </c>
       <c r="AB24" s="10">
         <v>5800</v>
@@ -4066,14 +4066,14 @@
       </c>
       <c r="AD24" s="11">
         <f t="shared" si="9"/>
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="AE24" s="3">
-        <v>4549</v>
+        <v>4550</v>
       </c>
       <c r="AF24" s="12">
         <f t="shared" si="10"/>
-        <v>0.78431034482758621</v>
+        <v>0.78448275862068961</v>
       </c>
       <c r="AG24" s="10">
         <v>5880</v>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="AI24" s="11">
         <f t="shared" si="11"/>
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="AJ24" s="3">
-        <v>4611</v>
+        <v>4612</v>
       </c>
       <c r="AK24" s="12">
         <f t="shared" si="12"/>
-        <v>0.78418367346938778</v>
+        <v>0.78435374149659864</v>
       </c>
       <c r="AL24" s="10">
         <v>5984</v>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="AN24" s="11">
         <f t="shared" si="13"/>
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="AO24" s="3">
-        <v>4666</v>
+        <v>4667</v>
       </c>
       <c r="AP24" s="12">
         <f t="shared" si="14"/>
-        <v>0.77974598930481287</v>
+        <v>0.77991310160427807</v>
       </c>
       <c r="AQ24" s="10">
         <v>6083</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="AS24" s="11">
         <f t="shared" si="15"/>
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="AT24" s="3">
-        <v>4735</v>
+        <v>4736</v>
       </c>
       <c r="AU24" s="12">
         <f t="shared" si="16"/>
-        <v>0.77839881637349995</v>
+        <v>0.77856320894295583</v>
       </c>
       <c r="AV24" s="10">
         <v>6170</v>
@@ -4134,14 +4134,14 @@
       </c>
       <c r="AX24" s="11">
         <f t="shared" si="17"/>
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="AY24" s="3">
-        <v>4765</v>
+        <v>4766</v>
       </c>
       <c r="AZ24" s="12">
         <f t="shared" si="18"/>
-        <v>0.77228525121555913</v>
+        <v>0.77244732576985409</v>
       </c>
       <c r="BA24" s="10">
         <v>6245</v>
@@ -4151,14 +4151,14 @@
       </c>
       <c r="BC24" s="11">
         <f t="shared" si="19"/>
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="BD24" s="3">
-        <v>4823</v>
+        <v>4824</v>
       </c>
       <c r="BE24" s="12">
         <f t="shared" si="20"/>
-        <v>0.77229783827061649</v>
+        <v>0.77245796637309849</v>
       </c>
       <c r="BF24" s="10">
         <v>6256</v>
@@ -4168,14 +4168,14 @@
       </c>
       <c r="BH24" s="11">
         <f t="shared" si="21"/>
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="BI24" s="3">
-        <v>4865</v>
+        <v>4866</v>
       </c>
       <c r="BJ24" s="12">
         <f t="shared" si="22"/>
-        <v>0.77765345268542196</v>
+        <v>0.77781329923273657</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4437,14 +4437,14 @@
       </c>
       <c r="O26" s="11">
         <f t="shared" si="3"/>
-        <v>6347</v>
+        <v>6348</v>
       </c>
       <c r="P26" s="3">
-        <v>20085</v>
+        <v>20086</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="4"/>
-        <v>0.80733981831336921</v>
+        <v>0.80738001447061658</v>
       </c>
       <c r="R26" s="10">
         <v>25640</v>
@@ -4454,14 +4454,14 @@
       </c>
       <c r="T26" s="11">
         <f t="shared" si="5"/>
-        <v>5651</v>
+        <v>5652</v>
       </c>
       <c r="U26" s="3">
-        <v>20653</v>
+        <v>20654</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="6"/>
-        <v>0.8054992199687987</v>
+        <v>0.80553822152886112</v>
       </c>
       <c r="W26" s="10">
         <v>25884</v>
@@ -4471,14 +4471,14 @@
       </c>
       <c r="Y26" s="11">
         <f t="shared" si="7"/>
-        <v>6420</v>
+        <v>6421</v>
       </c>
       <c r="Z26" s="3">
-        <v>20818</v>
+        <v>20819</v>
       </c>
       <c r="AA26" s="12">
         <f t="shared" si="8"/>
-        <v>0.80428063668675631</v>
+        <v>0.80431927059187147</v>
       </c>
       <c r="AB26" s="10">
         <v>26140</v>
@@ -4488,14 +4488,14 @@
       </c>
       <c r="AD26" s="11">
         <f t="shared" si="9"/>
-        <v>7479</v>
+        <v>7480</v>
       </c>
       <c r="AE26" s="3">
-        <v>20978</v>
+        <v>20979</v>
       </c>
       <c r="AF26" s="12">
         <f t="shared" si="10"/>
-        <v>0.80252486610558527</v>
+        <v>0.80256312165263965</v>
       </c>
       <c r="AG26" s="10">
         <v>26255</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="AN26" s="11">
         <f t="shared" si="13"/>
-        <v>6663</v>
+        <v>6664</v>
       </c>
       <c r="AO26" s="3">
-        <v>21055</v>
+        <v>21056</v>
       </c>
       <c r="AP26" s="12">
         <f t="shared" si="14"/>
-        <v>0.79883901809765911</v>
+        <v>0.79887695868270292</v>
       </c>
       <c r="AQ26" s="10">
         <v>26428</v>
@@ -4539,14 +4539,14 @@
       </c>
       <c r="AS26" s="11">
         <f t="shared" si="15"/>
-        <v>8148</v>
+        <v>8149</v>
       </c>
       <c r="AT26" s="3">
-        <v>21061</v>
+        <v>21062</v>
       </c>
       <c r="AU26" s="12">
         <f t="shared" si="16"/>
-        <v>0.7969199334039655</v>
+        <v>0.79695777205993645</v>
       </c>
       <c r="AV26" s="10">
         <v>26536</v>
@@ -4617,11 +4617,11 @@
         <v>119095</v>
       </c>
       <c r="F27" s="3">
-        <v>119355</v>
+        <v>119356</v>
       </c>
       <c r="G27" s="12">
         <f t="shared" si="0"/>
-        <v>0.7560669694608616</v>
+        <v>0.75607330406745088</v>
       </c>
       <c r="H27" s="10">
         <v>159240</v>
@@ -4631,14 +4631,14 @@
       </c>
       <c r="J27" s="11">
         <f t="shared" si="1"/>
-        <v>52402</v>
+        <v>52403</v>
       </c>
       <c r="K27" s="3">
-        <v>120253</v>
+        <v>120254</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="2"/>
-        <v>0.75516829942225572</v>
+        <v>0.75517457925144438</v>
       </c>
       <c r="M27" s="10">
         <v>161175</v>
@@ -4648,14 +4648,14 @@
       </c>
       <c r="O27" s="11">
         <f t="shared" si="3"/>
-        <v>51226</v>
+        <v>51227</v>
       </c>
       <c r="P27" s="3">
-        <v>121474</v>
+        <v>121475</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="4"/>
-        <v>0.75367767954087173</v>
+        <v>0.75368388397704356</v>
       </c>
       <c r="R27" s="10">
         <v>163738</v>
@@ -4665,14 +4665,14 @@
       </c>
       <c r="T27" s="11">
         <f t="shared" si="5"/>
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="U27" s="3">
-        <v>123213</v>
+        <v>123214</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="6"/>
-        <v>0.75250094663425715</v>
+        <v>0.75250705395204531</v>
       </c>
       <c r="W27" s="10">
         <v>165285</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="Y27" s="11">
         <f t="shared" si="7"/>
-        <v>54512</v>
+        <v>54513</v>
       </c>
       <c r="Z27" s="3">
-        <v>124683</v>
+        <v>124684</v>
       </c>
       <c r="AA27" s="12">
         <f t="shared" si="8"/>
-        <v>0.75435157455304469</v>
+        <v>0.75435762470883627</v>
       </c>
       <c r="AB27" s="10">
         <v>167059</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="AD27" s="11">
         <f t="shared" si="9"/>
-        <v>63482</v>
+        <v>63483</v>
       </c>
       <c r="AE27" s="3">
-        <v>126165</v>
+        <v>126166</v>
       </c>
       <c r="AF27" s="12">
         <f t="shared" si="10"/>
-        <v>0.75521223040961571</v>
+        <v>0.75521821631878561</v>
       </c>
       <c r="AG27" s="10">
         <v>167755</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="AI27" s="11">
         <f t="shared" si="11"/>
-        <v>54798</v>
+        <v>54799</v>
       </c>
       <c r="AJ27" s="3">
-        <v>127107</v>
+        <v>127108</v>
       </c>
       <c r="AK27" s="12">
         <f t="shared" si="12"/>
-        <v>0.7576942565050222</v>
+        <v>0.7577002175792078</v>
       </c>
       <c r="AL27" s="10">
         <v>166641</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="AN27" s="11">
         <f t="shared" si="13"/>
-        <v>50764</v>
+        <v>50765</v>
       </c>
       <c r="AO27" s="3">
-        <v>128427</v>
+        <v>128428</v>
       </c>
       <c r="AP27" s="12">
         <f t="shared" si="14"/>
-        <v>0.77068068482546315</v>
+        <v>0.77068668574960542</v>
       </c>
       <c r="AQ27" s="10">
         <v>146205</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AS27" s="11">
         <f t="shared" si="15"/>
-        <v>56461</v>
+        <v>56463</v>
       </c>
       <c r="AT27" s="3">
-        <v>128848</v>
+        <v>128850</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="16"/>
-        <v>0.88128312985192025</v>
+        <v>0.8812968092746486</v>
       </c>
       <c r="AV27" s="10">
         <v>144136</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AX27" s="11">
         <f t="shared" si="17"/>
-        <v>38975</v>
+        <v>38977</v>
       </c>
       <c r="AY27" s="3">
-        <v>129615</v>
+        <v>129617</v>
       </c>
       <c r="AZ27" s="12">
         <f t="shared" si="18"/>
-        <v>0.8992548704001776</v>
+        <v>0.89926874618415942</v>
       </c>
       <c r="BA27" s="10">
         <v>144942</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="BC27" s="11">
         <f t="shared" si="19"/>
-        <v>48739</v>
+        <v>48741</v>
       </c>
       <c r="BD27" s="3">
-        <v>130842</v>
+        <v>130844</v>
       </c>
       <c r="BE27" s="12">
         <f t="shared" si="20"/>
-        <v>0.90271970857308437</v>
+        <v>0.90273350719598189</v>
       </c>
       <c r="BF27" s="10">
         <v>145908</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="BH27" s="11">
         <f t="shared" si="21"/>
-        <v>123829</v>
+        <v>123831</v>
       </c>
       <c r="BI27" s="3">
-        <v>131305</v>
+        <v>131307</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="22"/>
-        <v>0.89991638566768095</v>
+        <v>0.89993009293527426</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5053,14 +5053,14 @@
       </c>
       <c r="J29" s="11">
         <f t="shared" si="1"/>
-        <v>44429</v>
+        <v>44430</v>
       </c>
       <c r="K29" s="3">
-        <v>128117</v>
+        <v>128118</v>
       </c>
       <c r="L29" s="12">
         <f t="shared" si="2"/>
-        <v>0.86243293639307184</v>
+        <v>0.86243966799728045</v>
       </c>
       <c r="M29" s="10">
         <v>149800</v>
@@ -5070,14 +5070,14 @@
       </c>
       <c r="O29" s="11">
         <f t="shared" si="3"/>
-        <v>41911</v>
+        <v>41912</v>
       </c>
       <c r="P29" s="3">
-        <v>128931</v>
+        <v>128932</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="4"/>
-        <v>0.86068758344459284</v>
+        <v>0.86069425901201602</v>
       </c>
       <c r="R29" s="10">
         <v>151023</v>
@@ -5087,14 +5087,14 @@
       </c>
       <c r="T29" s="11">
         <f t="shared" si="5"/>
-        <v>35745</v>
+        <v>35746</v>
       </c>
       <c r="U29" s="3">
-        <v>130239</v>
+        <v>130240</v>
       </c>
       <c r="V29" s="12">
         <f t="shared" si="6"/>
-        <v>0.86237857809737595</v>
+        <v>0.86238519960535809</v>
       </c>
       <c r="W29" s="10">
         <v>151285</v>
@@ -5104,14 +5104,14 @@
       </c>
       <c r="Y29" s="11">
         <f t="shared" si="7"/>
-        <v>46514</v>
+        <v>46515</v>
       </c>
       <c r="Z29" s="3">
-        <v>131369</v>
+        <v>131370</v>
       </c>
       <c r="AA29" s="12">
         <f t="shared" si="8"/>
-        <v>0.8683544303797468</v>
+        <v>0.86836104042039863</v>
       </c>
       <c r="AB29" s="10">
         <v>151326</v>
@@ -5121,14 +5121,14 @@
       </c>
       <c r="AD29" s="11">
         <f t="shared" si="9"/>
-        <v>52814</v>
+        <v>52815</v>
       </c>
       <c r="AE29" s="3">
-        <v>132472</v>
+        <v>132473</v>
       </c>
       <c r="AF29" s="12">
         <f t="shared" si="10"/>
-        <v>0.87540805942138167</v>
+        <v>0.87541466767112064</v>
       </c>
       <c r="AG29" s="10">
         <v>151778</v>
@@ -5138,14 +5138,14 @@
       </c>
       <c r="AI29" s="11">
         <f t="shared" si="11"/>
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="AJ29" s="3">
-        <v>133872</v>
+        <v>133873</v>
       </c>
       <c r="AK29" s="12">
         <f t="shared" si="12"/>
-        <v>0.88202506292084493</v>
+        <v>0.88203165149099338</v>
       </c>
       <c r="AL29" s="10">
         <v>148226</v>
@@ -5155,14 +5155,14 @@
       </c>
       <c r="AN29" s="11">
         <f t="shared" si="13"/>
-        <v>29513</v>
+        <v>29514</v>
       </c>
       <c r="AO29" s="3">
-        <v>134751</v>
+        <v>134752</v>
       </c>
       <c r="AP29" s="12">
         <f t="shared" si="14"/>
-        <v>0.90909152240497615</v>
+        <v>0.90909826885971423</v>
       </c>
       <c r="AQ29" s="10">
         <v>147404</v>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="AS29" s="11">
         <f t="shared" si="15"/>
-        <v>44242</v>
+        <v>44243</v>
       </c>
       <c r="AT29" s="3">
-        <v>135434</v>
+        <v>135435</v>
       </c>
       <c r="AU29" s="12">
         <f t="shared" si="16"/>
-        <v>0.91879460530243418</v>
+        <v>0.91880138937884992</v>
       </c>
       <c r="AV29" s="10">
         <v>144908</v>
@@ -5189,14 +5189,14 @@
       </c>
       <c r="AX29" s="11">
         <f t="shared" si="17"/>
-        <v>27053</v>
+        <v>27054</v>
       </c>
       <c r="AY29" s="3">
-        <v>136291</v>
+        <v>136292</v>
       </c>
       <c r="AZ29" s="12">
         <f t="shared" si="18"/>
-        <v>0.94053468407541341</v>
+        <v>0.94054158500565876</v>
       </c>
       <c r="BA29" s="10">
         <v>142935</v>
@@ -5206,14 +5206,14 @@
       </c>
       <c r="BC29" s="11">
         <f t="shared" si="19"/>
-        <v>37908</v>
+        <v>37909</v>
       </c>
       <c r="BD29" s="3">
-        <v>137083</v>
+        <v>137084</v>
       </c>
       <c r="BE29" s="12">
         <f t="shared" si="20"/>
-        <v>0.95905831321929547</v>
+        <v>0.95906530940637358</v>
       </c>
       <c r="BF29" s="10">
         <v>143561</v>
@@ -5250,11 +5250,11 @@
         <v>192952</v>
       </c>
       <c r="F30" s="3">
-        <v>193170</v>
+        <v>193171</v>
       </c>
       <c r="G30" s="12">
         <f t="shared" si="0"/>
-        <v>0.88195814157352614</v>
+        <v>0.88196270728322013</v>
       </c>
       <c r="H30" s="10">
         <v>219645</v>
@@ -5264,14 +5264,14 @@
       </c>
       <c r="J30" s="11">
         <f t="shared" si="1"/>
-        <v>67236</v>
+        <v>67237</v>
       </c>
       <c r="K30" s="3">
-        <v>194747</v>
+        <v>194748</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="2"/>
-        <v>0.88664435794122332</v>
+        <v>0.88664891074233421</v>
       </c>
       <c r="M30" s="10">
         <v>219769</v>
@@ -5543,14 +5543,14 @@
       </c>
       <c r="AD31" s="11">
         <f t="shared" si="9"/>
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="AE31" s="3">
-        <v>98718</v>
+        <v>98719</v>
       </c>
       <c r="AF31" s="12">
         <f t="shared" si="10"/>
-        <v>0.91866589737385773</v>
+        <v>0.91867520333525654</v>
       </c>
       <c r="AG31" s="10">
         <v>107867</v>
@@ -5560,14 +5560,14 @@
       </c>
       <c r="AI31" s="11">
         <f t="shared" si="11"/>
-        <v>40922</v>
+        <v>40923</v>
       </c>
       <c r="AJ31" s="3">
-        <v>99574</v>
+        <v>99575</v>
       </c>
       <c r="AK31" s="12">
         <f t="shared" si="12"/>
-        <v>0.92311828455412681</v>
+        <v>0.92312755523005185</v>
       </c>
       <c r="AL31" s="10">
         <v>106953</v>
@@ -5628,14 +5628,14 @@
       </c>
       <c r="BC31" s="11">
         <f t="shared" si="19"/>
-        <v>34948</v>
+        <v>34949</v>
       </c>
       <c r="BD31" s="3">
-        <v>102146</v>
+        <v>102147</v>
       </c>
       <c r="BE31" s="12">
         <f t="shared" si="20"/>
-        <v>0.96721839254601927</v>
+        <v>0.967227861525642</v>
       </c>
       <c r="BF31" s="10">
         <v>107069</v>
@@ -5883,11 +5883,11 @@
         <v>798628</v>
       </c>
       <c r="F33" s="3">
-        <v>798878</v>
+        <v>798881</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="0"/>
-        <v>0.91929455519601566</v>
+        <v>0.91929800739230294</v>
       </c>
       <c r="H33" s="10">
         <v>871303</v>
@@ -5897,14 +5897,14 @@
       </c>
       <c r="J33" s="11">
         <f t="shared" si="1"/>
-        <v>172522</v>
+        <v>172525</v>
       </c>
       <c r="K33" s="3">
-        <v>805157</v>
+        <v>805160</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="2"/>
-        <v>0.92408381470051171</v>
+        <v>0.92408725781961043</v>
       </c>
       <c r="M33" s="10">
         <v>877062</v>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="O33" s="11">
         <f t="shared" si="3"/>
-        <v>162007</v>
+        <v>162011</v>
       </c>
       <c r="P33" s="3">
-        <v>810235</v>
+        <v>810239</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="4"/>
-        <v>0.92380584268843025</v>
+        <v>0.9238104033694311</v>
       </c>
       <c r="R33" s="10">
         <v>881026</v>
@@ -5931,14 +5931,14 @@
       </c>
       <c r="T33" s="11">
         <f t="shared" si="5"/>
-        <v>137073</v>
+        <v>137076</v>
       </c>
       <c r="U33" s="3">
-        <v>816384</v>
+        <v>816387</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="6"/>
-        <v>0.92662872605348767</v>
+        <v>0.9266321311743354</v>
       </c>
       <c r="W33" s="10">
         <v>884173</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="Y33" s="11">
         <f t="shared" si="7"/>
-        <v>177138</v>
+        <v>177142</v>
       </c>
       <c r="Z33" s="3">
-        <v>820956</v>
+        <v>820960</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>0.92850154890502201</v>
+        <v>0.92850607290654652</v>
       </c>
       <c r="AB33" s="10">
         <v>884817</v>
@@ -5965,14 +5965,14 @@
       </c>
       <c r="AD33" s="11">
         <f t="shared" si="9"/>
-        <v>222677</v>
+        <v>222681</v>
       </c>
       <c r="AE33" s="3">
-        <v>826032</v>
+        <v>826036</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="10"/>
-        <v>0.93356253326959138</v>
+        <v>0.93356705397839324</v>
       </c>
       <c r="AG33" s="10">
         <v>888089</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="AI33" s="11">
         <f t="shared" si="11"/>
-        <v>209160</v>
+        <v>209164</v>
       </c>
       <c r="AJ33" s="3">
-        <v>829774</v>
+        <v>829778</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="12"/>
-        <v>0.93433653609041434</v>
+        <v>0.93434104014349917</v>
       </c>
       <c r="AL33" s="10">
         <v>887648</v>
@@ -5999,14 +5999,14 @@
       </c>
       <c r="AN33" s="11">
         <f t="shared" si="13"/>
-        <v>110959</v>
+        <v>110962</v>
       </c>
       <c r="AO33" s="3">
-        <v>833658</v>
+        <v>833661</v>
       </c>
       <c r="AP33" s="12">
         <f t="shared" si="14"/>
-        <v>0.93917634017087859</v>
+        <v>0.93917971988896498</v>
       </c>
       <c r="AQ33" s="10">
         <v>877839</v>
@@ -6016,14 +6016,14 @@
       </c>
       <c r="AS33" s="11">
         <f t="shared" si="15"/>
-        <v>210340</v>
+        <v>210342</v>
       </c>
       <c r="AT33" s="3">
-        <v>841917</v>
+        <v>841919</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="16"/>
-        <v>0.95907905663794846</v>
+        <v>0.95908133496005532</v>
       </c>
       <c r="AV33" s="10">
         <v>881788</v>
@@ -6033,14 +6033,14 @@
       </c>
       <c r="AX33" s="11">
         <f t="shared" si="17"/>
-        <v>121433</v>
+        <v>121435</v>
       </c>
       <c r="AY33" s="3">
-        <v>847609</v>
+        <v>847611</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="18"/>
-        <v>0.96123898261260077</v>
+        <v>0.96124125073146838</v>
       </c>
       <c r="BA33" s="10">
         <v>886741</v>
@@ -6050,14 +6050,14 @@
       </c>
       <c r="BC33" s="11">
         <f t="shared" si="19"/>
-        <v>139175</v>
+        <v>139178</v>
       </c>
       <c r="BD33" s="3">
-        <v>853501</v>
+        <v>853504</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="20"/>
-        <v>0.96251442078352079</v>
+        <v>0.96251780395854036</v>
       </c>
       <c r="BF33" s="10">
         <v>893063</v>
@@ -6067,14 +6067,14 @@
       </c>
       <c r="BH33" s="11">
         <f t="shared" si="21"/>
-        <v>834012</v>
+        <v>834014</v>
       </c>
       <c r="BI33" s="3">
-        <v>857135</v>
+        <v>857137</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="22"/>
-        <v>0.95976991544829426</v>
+        <v>0.95977215493195889</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6516,11 +6516,11 @@
         <v>1213488</v>
       </c>
       <c r="F36" s="3">
-        <v>1214468</v>
+        <v>1214469</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="0"/>
-        <v>0.87391477361449021</v>
+        <v>0.87391549320098694</v>
       </c>
       <c r="H36" s="10">
         <v>1398033</v>
@@ -6530,14 +6530,14 @@
       </c>
       <c r="J36" s="11">
         <f t="shared" si="1"/>
-        <v>374682</v>
+        <v>374683</v>
       </c>
       <c r="K36" s="3">
-        <v>1219847</v>
+        <v>1219848</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="2"/>
-        <v>0.87254521173677591</v>
+        <v>0.87254592702747358</v>
       </c>
       <c r="M36" s="10">
         <v>1405014</v>
@@ -6547,14 +6547,14 @@
       </c>
       <c r="O36" s="11">
         <f t="shared" si="3"/>
-        <v>355861</v>
+        <v>355862</v>
       </c>
       <c r="P36" s="3">
-        <v>1224773</v>
+        <v>1224774</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="4"/>
-        <v>0.87171586902336917</v>
+        <v>0.87171658076004932</v>
       </c>
       <c r="R36" s="10">
         <v>1409335</v>
@@ -6598,14 +6598,14 @@
       </c>
       <c r="AD36" s="11">
         <f t="shared" si="9"/>
-        <v>476498</v>
+        <v>476499</v>
       </c>
       <c r="AE36" s="3">
-        <v>1244831</v>
+        <v>1244832</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="10"/>
-        <v>0.87854775043598121</v>
+        <v>0.87854845619262645</v>
       </c>
       <c r="AG36" s="10">
         <v>1419473</v>
@@ -6615,14 +6615,14 @@
       </c>
       <c r="AI36" s="11">
         <f t="shared" si="11"/>
-        <v>414510</v>
+        <v>414512</v>
       </c>
       <c r="AJ36" s="3">
-        <v>1251119</v>
+        <v>1251121</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="12"/>
-        <v>0.88139682825950194</v>
+        <v>0.88139823723311395</v>
       </c>
       <c r="AL36" s="10">
         <v>1415447</v>
@@ -6632,14 +6632,14 @@
       </c>
       <c r="AN36" s="11">
         <f t="shared" si="13"/>
-        <v>261122</v>
+        <v>261124</v>
       </c>
       <c r="AO36" s="3">
-        <v>1259387</v>
+        <v>1259389</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="14"/>
-        <v>0.88974507699687799</v>
+        <v>0.88974648997807759</v>
       </c>
       <c r="AQ36" s="10">
         <v>1379433</v>
@@ -6649,14 +6649,14 @@
       </c>
       <c r="AS36" s="11">
         <f t="shared" si="15"/>
-        <v>413106</v>
+        <v>413109</v>
       </c>
       <c r="AT36" s="3">
-        <v>1269279</v>
+        <v>1269282</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="16"/>
-        <v>0.92014545106576395</v>
+        <v>0.92014762587236931</v>
       </c>
       <c r="AV36" s="10">
         <v>1370415</v>
@@ -6666,14 +6666,14 @@
       </c>
       <c r="AX36" s="11">
         <f t="shared" si="17"/>
-        <v>275214</v>
+        <v>275217</v>
       </c>
       <c r="AY36" s="3">
-        <v>1275424</v>
+        <v>1275427</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="18"/>
-        <v>0.93068450068045083</v>
+        <v>0.93068668979834579</v>
       </c>
       <c r="BA36" s="10">
         <v>1375391</v>
@@ -6683,14 +6683,14 @@
       </c>
       <c r="BC36" s="11">
         <f t="shared" si="19"/>
-        <v>338581</v>
+        <v>338583</v>
       </c>
       <c r="BD36" s="3">
-        <v>1281947</v>
+        <v>1281949</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="20"/>
-        <v>0.93206004692483813</v>
+        <v>0.93206150105679042</v>
       </c>
       <c r="BF36" s="10">
         <v>1380633</v>
@@ -6700,14 +6700,14 @@
       </c>
       <c r="BH36" s="11">
         <f t="shared" si="21"/>
-        <v>1217311</v>
+        <v>1217313</v>
       </c>
       <c r="BI36" s="3">
-        <v>1281466</v>
+        <v>1281468</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="22"/>
-        <v>0.92817280189594198</v>
+        <v>0.92817425050683278</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6727,11 +6727,11 @@
         <v>627302</v>
       </c>
       <c r="F37" s="3">
-        <v>627971</v>
+        <v>627974</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="0"/>
-        <v>0.88628370291753233</v>
+        <v>0.88628793695239816</v>
       </c>
       <c r="H37" s="10">
         <v>707340</v>
@@ -6741,14 +6741,14 @@
       </c>
       <c r="J37" s="11">
         <f t="shared" si="1"/>
-        <v>167235</v>
+        <v>167238</v>
       </c>
       <c r="K37" s="3">
-        <v>632198</v>
+        <v>632201</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="2"/>
-        <v>0.89376820199621121</v>
+        <v>0.89377244323804672</v>
       </c>
       <c r="M37" s="10">
         <v>710827</v>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="O37" s="11">
         <f t="shared" si="3"/>
-        <v>160114</v>
+        <v>160118</v>
       </c>
       <c r="P37" s="3">
-        <v>636971</v>
+        <v>636975</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="4"/>
-        <v>0.89609848809907333</v>
+        <v>0.89610411534733492</v>
       </c>
       <c r="R37" s="10">
         <v>713357</v>
@@ -6775,14 +6775,14 @@
       </c>
       <c r="T37" s="11">
         <f t="shared" si="5"/>
-        <v>137615</v>
+        <v>137619</v>
       </c>
       <c r="U37" s="3">
-        <v>644569</v>
+        <v>644573</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="6"/>
-        <v>0.90357142356491915</v>
+        <v>0.90357703085551833</v>
       </c>
       <c r="W37" s="10">
         <v>709504</v>
@@ -6792,14 +6792,14 @@
       </c>
       <c r="Y37" s="11">
         <f t="shared" si="7"/>
-        <v>170680</v>
+        <v>170683</v>
       </c>
       <c r="Z37" s="3">
-        <v>650135</v>
+        <v>650138</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="8"/>
-        <v>0.9163232342594263</v>
+        <v>0.91632746256539777</v>
       </c>
       <c r="AB37" s="10">
         <v>709880</v>
@@ -6809,14 +6809,14 @@
       </c>
       <c r="AD37" s="11">
         <f t="shared" si="9"/>
-        <v>220786</v>
+        <v>220789</v>
       </c>
       <c r="AE37" s="3">
-        <v>655100</v>
+        <v>655103</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="10"/>
-        <v>0.92283202794838559</v>
+        <v>0.9228362540147631</v>
       </c>
       <c r="AG37" s="10">
         <v>716349</v>
@@ -6826,14 +6826,14 @@
       </c>
       <c r="AI37" s="11">
         <f t="shared" si="11"/>
-        <v>195312</v>
+        <v>195316</v>
       </c>
       <c r="AJ37" s="3">
-        <v>661858</v>
+        <v>661862</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="12"/>
-        <v>0.92393232907423617</v>
+        <v>0.92393791294466798</v>
       </c>
       <c r="AL37" s="10">
         <v>718037</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="AN37" s="11">
         <f t="shared" si="13"/>
-        <v>115179</v>
+        <v>115182</v>
       </c>
       <c r="AO37" s="3">
-        <v>668149</v>
+        <v>668152</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="14"/>
-        <v>0.93052168620837084</v>
+        <v>0.93052586426604755</v>
       </c>
       <c r="AQ37" s="10">
         <v>723207</v>
@@ -6860,14 +6860,14 @@
       </c>
       <c r="AS37" s="11">
         <f t="shared" si="15"/>
-        <v>201326</v>
+        <v>201329</v>
       </c>
       <c r="AT37" s="3">
-        <v>675769</v>
+        <v>675772</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="16"/>
-        <v>0.93440605525112452</v>
+        <v>0.93441020344106185</v>
       </c>
       <c r="AV37" s="10">
         <v>726054</v>
@@ -6877,14 +6877,14 @@
       </c>
       <c r="AX37" s="11">
         <f t="shared" si="17"/>
-        <v>124582</v>
+        <v>124586</v>
       </c>
       <c r="AY37" s="3">
-        <v>681068</v>
+        <v>681072</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="18"/>
-        <v>0.93804042123588605</v>
+        <v>0.93804593046798168</v>
       </c>
       <c r="BA37" s="10">
         <v>731853</v>
@@ -6894,14 +6894,14 @@
       </c>
       <c r="BC37" s="11">
         <f t="shared" si="19"/>
-        <v>136744</v>
+        <v>136747</v>
       </c>
       <c r="BD37" s="3">
-        <v>686379</v>
+        <v>686382</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="20"/>
-        <v>0.93786457116388122</v>
+        <v>0.9378686703477338</v>
       </c>
       <c r="BF37" s="10">
         <v>734800</v>
@@ -6911,14 +6911,14 @@
       </c>
       <c r="BH37" s="11">
         <f t="shared" si="21"/>
-        <v>630835</v>
+        <v>630838</v>
       </c>
       <c r="BI37" s="3">
-        <v>686241</v>
+        <v>686244</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="22"/>
-        <v>0.93391535111594992</v>
+        <v>0.93391943385955367</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7571,11 +7571,11 @@
         <v>762739</v>
       </c>
       <c r="F41" s="3">
-        <v>763716</v>
+        <v>763723</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="0"/>
-        <v>0.87102844668897517</v>
+        <v>0.87103643028382816</v>
       </c>
       <c r="H41" s="10">
         <v>885438</v>
@@ -7585,14 +7585,14 @@
       </c>
       <c r="J41" s="11">
         <f t="shared" si="1"/>
-        <v>217437</v>
+        <v>217445</v>
       </c>
       <c r="K41" s="3">
-        <v>768971</v>
+        <v>768979</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="2"/>
-        <v>0.8684639692445999</v>
+        <v>0.86847300432102525</v>
       </c>
       <c r="M41" s="10">
         <v>894344</v>
@@ -7602,14 +7602,14 @@
       </c>
       <c r="O41" s="11">
         <f t="shared" si="3"/>
-        <v>206491</v>
+        <v>206498</v>
       </c>
       <c r="P41" s="3">
-        <v>773435</v>
+        <v>773442</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="4"/>
-        <v>0.86480705410893344</v>
+        <v>0.86481488107484372</v>
       </c>
       <c r="R41" s="10">
         <v>899235</v>
@@ -7619,14 +7619,14 @@
       </c>
       <c r="T41" s="11">
         <f t="shared" si="5"/>
-        <v>170818</v>
+        <v>170829</v>
       </c>
       <c r="U41" s="3">
-        <v>780275</v>
+        <v>780286</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="6"/>
-        <v>0.86770977553142392</v>
+        <v>0.86772200815137313</v>
       </c>
       <c r="W41" s="10">
         <v>900188</v>
@@ -7636,14 +7636,14 @@
       </c>
       <c r="Y41" s="11">
         <f t="shared" si="7"/>
-        <v>227482</v>
+        <v>227494</v>
       </c>
       <c r="Z41" s="3">
-        <v>786278</v>
+        <v>786290</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="8"/>
-        <v>0.87345976618217525</v>
+        <v>0.87347309673090512</v>
       </c>
       <c r="AB41" s="10">
         <v>900385</v>
@@ -7653,14 +7653,14 @@
       </c>
       <c r="AD41" s="11">
         <f t="shared" si="9"/>
-        <v>278325</v>
+        <v>278338</v>
       </c>
       <c r="AE41" s="3">
-        <v>790843</v>
+        <v>790856</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="10"/>
-        <v>0.878338710662661</v>
+        <v>0.87835314893073524</v>
       </c>
       <c r="AG41" s="10">
         <v>896586</v>
@@ -7670,14 +7670,14 @@
       </c>
       <c r="AI41" s="11">
         <f t="shared" si="11"/>
-        <v>232877</v>
+        <v>232888</v>
       </c>
       <c r="AJ41" s="3">
-        <v>796687</v>
+        <v>796698</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="12"/>
-        <v>0.88857845203917973</v>
+        <v>0.88859072080090473</v>
       </c>
       <c r="AL41" s="10">
         <v>888836</v>
@@ -7687,14 +7687,14 @@
       </c>
       <c r="AN41" s="11">
         <f t="shared" si="13"/>
-        <v>137000</v>
+        <v>137010</v>
       </c>
       <c r="AO41" s="3">
-        <v>802525</v>
+        <v>802535</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="14"/>
-        <v>0.90289434721365924</v>
+        <v>0.90290559788307401</v>
       </c>
       <c r="AQ41" s="10">
         <v>877850</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="AS41" s="11">
         <f t="shared" si="15"/>
-        <v>256456</v>
+        <v>256468</v>
       </c>
       <c r="AT41" s="3">
-        <v>809994</v>
+        <v>810006</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="16"/>
-        <v>0.92270205615993617</v>
+        <v>0.92271572592128492</v>
       </c>
       <c r="AV41" s="10">
         <v>870770</v>
@@ -7721,14 +7721,14 @@
       </c>
       <c r="AX41" s="11">
         <f t="shared" si="17"/>
-        <v>141894</v>
+        <v>141910</v>
       </c>
       <c r="AY41" s="3">
-        <v>814252</v>
+        <v>814268</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="18"/>
-        <v>0.93509422694856281</v>
+        <v>0.93511260149063469</v>
       </c>
       <c r="BA41" s="10">
         <v>867846</v>
@@ -7738,14 +7738,14 @@
       </c>
       <c r="BC41" s="11">
         <f t="shared" si="19"/>
-        <v>163704</v>
+        <v>163719</v>
       </c>
       <c r="BD41" s="3">
-        <v>820760</v>
+        <v>820775</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="20"/>
-        <v>0.94574383012654317</v>
+        <v>0.94576111429908072</v>
       </c>
       <c r="BF41" s="10">
         <v>876639</v>
@@ -7755,14 +7755,14 @@
       </c>
       <c r="BH41" s="11">
         <f t="shared" si="21"/>
-        <v>773524</v>
+        <v>773542</v>
       </c>
       <c r="BI41" s="3">
-        <v>823847</v>
+        <v>823865</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="22"/>
-        <v>0.93977908808528943</v>
+        <v>0.93979962105267956</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7993,11 +7993,11 @@
         <v>3341</v>
       </c>
       <c r="F43" s="3">
-        <v>3351</v>
+        <v>3353</v>
       </c>
       <c r="G43" s="12">
         <f t="shared" si="0"/>
-        <v>0.89622893821877503</v>
+        <v>0.89676384059909064</v>
       </c>
       <c r="H43" s="10">
         <v>3772</v>
@@ -8007,14 +8007,14 @@
       </c>
       <c r="J43" s="11">
         <f t="shared" si="1"/>
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="K43" s="3">
-        <v>3356</v>
+        <v>3358</v>
       </c>
       <c r="L43" s="12">
         <f t="shared" si="2"/>
-        <v>0.88971367974549309</v>
+        <v>0.8902439024390244</v>
       </c>
       <c r="M43" s="10">
         <v>3826</v>
@@ -8024,14 +8024,14 @@
       </c>
       <c r="O43" s="11">
         <f t="shared" si="3"/>
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="P43" s="3">
-        <v>3379</v>
+        <v>3381</v>
       </c>
       <c r="Q43" s="12">
         <f t="shared" si="4"/>
-        <v>0.88316779926816513</v>
+        <v>0.88369053842132772</v>
       </c>
       <c r="R43" s="10">
         <v>3887</v>
@@ -8041,14 +8041,14 @@
       </c>
       <c r="T43" s="11">
         <f t="shared" si="5"/>
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="U43" s="3">
-        <v>3398</v>
+        <v>3400</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="6"/>
-        <v>0.87419603807563673</v>
+        <v>0.87471057370722927</v>
       </c>
       <c r="W43" s="10">
         <v>3955</v>
@@ -8058,14 +8058,14 @@
       </c>
       <c r="Y43" s="11">
         <f t="shared" si="7"/>
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="Z43" s="3">
-        <v>3418</v>
+        <v>3420</v>
       </c>
       <c r="AA43" s="12">
         <f t="shared" si="8"/>
-        <v>0.86422250316055627</v>
+        <v>0.86472819216182051</v>
       </c>
       <c r="AB43" s="10">
         <v>3994</v>
@@ -8075,14 +8075,14 @@
       </c>
       <c r="AD43" s="11">
         <f t="shared" si="9"/>
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="AE43" s="3">
-        <v>3435</v>
+        <v>3437</v>
       </c>
       <c r="AF43" s="12">
         <f t="shared" si="10"/>
-        <v>0.86004006009013523</v>
+        <v>0.86054081121682524</v>
       </c>
       <c r="AG43" s="10">
         <v>4062</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="AI43" s="11">
         <f t="shared" si="11"/>
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="AJ43" s="3">
-        <v>3475</v>
+        <v>3477</v>
       </c>
       <c r="AK43" s="12">
         <f t="shared" si="12"/>
-        <v>0.85548990645002465</v>
+        <v>0.85598227474150668</v>
       </c>
       <c r="AL43" s="10">
         <v>4104</v>
@@ -8109,14 +8109,14 @@
       </c>
       <c r="AN43" s="11">
         <f t="shared" si="13"/>
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="AO43" s="3">
-        <v>3514</v>
+        <v>3516</v>
       </c>
       <c r="AP43" s="12">
         <f t="shared" si="14"/>
-        <v>0.85623781676413258</v>
+        <v>0.85672514619883045</v>
       </c>
       <c r="AQ43" s="10">
         <v>4090</v>
@@ -8126,14 +8126,14 @@
       </c>
       <c r="AS43" s="11">
         <f t="shared" si="15"/>
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="AT43" s="3">
-        <v>3534</v>
+        <v>3536</v>
       </c>
       <c r="AU43" s="12">
         <f t="shared" si="16"/>
-        <v>0.86405867970660144</v>
+        <v>0.86454767726161375</v>
       </c>
       <c r="AV43" s="10">
         <v>3783</v>
@@ -8143,14 +8143,14 @@
       </c>
       <c r="AX43" s="11">
         <f t="shared" si="17"/>
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="AY43" s="3">
-        <v>3533</v>
+        <v>3535</v>
       </c>
       <c r="AZ43" s="12">
         <f t="shared" si="18"/>
-        <v>0.93391488236849063</v>
+        <v>0.9344435633095427</v>
       </c>
       <c r="BA43" s="10">
         <v>3822</v>
@@ -8160,14 +8160,14 @@
       </c>
       <c r="BC43" s="11">
         <f t="shared" si="19"/>
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="BD43" s="3">
-        <v>3561</v>
+        <v>3563</v>
       </c>
       <c r="BE43" s="12">
         <f t="shared" si="20"/>
-        <v>0.93171114599686033</v>
+        <v>0.93223443223443225</v>
       </c>
       <c r="BF43" s="10">
         <v>3877</v>
@@ -8177,14 +8177,14 @@
       </c>
       <c r="BH43" s="11">
         <f t="shared" si="21"/>
-        <v>3438</v>
+        <v>3440</v>
       </c>
       <c r="BI43" s="3">
-        <v>3577</v>
+        <v>3579</v>
       </c>
       <c r="BJ43" s="12">
         <f t="shared" si="22"/>
-        <v>0.92262058292494198</v>
+        <v>0.9231364457054424</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8388,14 +8388,14 @@
       </c>
       <c r="BH44" s="11">
         <f t="shared" si="21"/>
-        <v>278264</v>
+        <v>278265</v>
       </c>
       <c r="BI44" s="3">
-        <v>306791</v>
+        <v>306792</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="22"/>
-        <v>0.85739158624891354</v>
+        <v>0.85739438095797038</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8429,14 +8429,14 @@
       </c>
       <c r="J45" s="11">
         <f t="shared" si="1"/>
-        <v>73565</v>
+        <v>73566</v>
       </c>
       <c r="K45" s="3">
-        <v>243494</v>
+        <v>243495</v>
       </c>
       <c r="L45" s="12">
         <f t="shared" si="2"/>
-        <v>0.87021192952360527</v>
+        <v>0.8702155033772917</v>
       </c>
       <c r="M45" s="10">
         <v>281946</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="O45" s="11">
         <f t="shared" si="3"/>
-        <v>68013</v>
+        <v>68014</v>
       </c>
       <c r="P45" s="3">
-        <v>245104</v>
+        <v>245105</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="4"/>
-        <v>0.86932958793527837</v>
+        <v>0.86933313471373952</v>
       </c>
       <c r="R45" s="10">
         <v>285278</v>
@@ -8514,14 +8514,14 @@
       </c>
       <c r="AI45" s="11">
         <f t="shared" si="11"/>
-        <v>80953</v>
+        <v>80954</v>
       </c>
       <c r="AJ45" s="3">
-        <v>251718</v>
+        <v>251719</v>
       </c>
       <c r="AK45" s="12">
         <f t="shared" si="12"/>
-        <v>0.87429708692677199</v>
+        <v>0.87430056024646674</v>
       </c>
       <c r="AL45" s="10">
         <v>286336</v>
@@ -9025,15 +9025,15 @@
       </c>
       <c r="E48" s="7">
         <f t="shared" ref="E48" si="23">F48-D48</f>
-        <v>2915150</v>
+        <v>2915172</v>
       </c>
       <c r="F48" s="8">
         <f>SUM(F10:F47)</f>
-        <v>8977128</v>
+        <v>8977150</v>
       </c>
       <c r="G48" s="5">
         <f>F48/C48</f>
-        <v>0.8772455215627627</v>
+        <v>0.87724767140416793</v>
       </c>
       <c r="H48" s="6">
         <f>SUM(H10:H47)</f>
@@ -9045,15 +9045,15 @@
       </c>
       <c r="J48" s="7">
         <f>K48-I48</f>
-        <v>2520100</v>
+        <v>2520125</v>
       </c>
       <c r="K48" s="8">
         <f>SUM(K10:K47)</f>
-        <v>9038508</v>
+        <v>9038533</v>
       </c>
       <c r="L48" s="5">
         <f>K48/H48</f>
-        <v>0.87871404248642071</v>
+        <v>0.87871647295957644</v>
       </c>
       <c r="M48" s="6">
         <f>SUM(M10:M47)</f>
@@ -9065,15 +9065,15 @@
       </c>
       <c r="O48" s="7">
         <f>P48-N48</f>
-        <v>2400908</v>
+        <v>2400935</v>
       </c>
       <c r="P48" s="8">
         <f>SUM(P10:P47)</f>
-        <v>9089572</v>
+        <v>9089599</v>
       </c>
       <c r="Q48" s="5">
         <f>P48/M48</f>
-        <v>0.87750742175504148</v>
+        <v>0.87751002833545999</v>
       </c>
       <c r="R48" s="6">
         <f>SUM(R10:R47)</f>
@@ -9085,15 +9085,15 @@
       </c>
       <c r="T48" s="7">
         <f>U48-S48</f>
-        <v>2087916</v>
+        <v>2087944</v>
       </c>
       <c r="U48" s="8">
         <f>SUM(U10:U47)</f>
-        <v>9168391</v>
+        <v>9168419</v>
       </c>
       <c r="V48" s="5">
         <f>U48/R48</f>
-        <v>0.87931334771043979</v>
+        <v>0.87931603310788142</v>
       </c>
       <c r="W48" s="6">
         <f>SUM(W10:W47)</f>
@@ -9105,15 +9105,15 @@
       </c>
       <c r="Y48" s="7">
         <f>Z48-X48</f>
-        <v>2662424</v>
+        <v>2662453</v>
       </c>
       <c r="Z48" s="8">
         <f>SUM(Z10:Z47)</f>
-        <v>9229643</v>
+        <v>9229672</v>
       </c>
       <c r="AA48" s="5">
         <f>Z48/W48</f>
-        <v>0.8827218072567895</v>
+        <v>0.8827245808128642</v>
       </c>
       <c r="AB48" s="6">
         <f>SUM(AB10:AB47)</f>
@@ -9125,15 +9125,15 @@
       </c>
       <c r="AD48" s="7">
         <f>AE48-AC48</f>
-        <v>3305637</v>
+        <v>3305669</v>
       </c>
       <c r="AE48" s="8">
         <f>SUM(AE10:AE47)</f>
-        <v>9295990</v>
+        <v>9296022</v>
       </c>
       <c r="AF48" s="5">
         <f>AE48/AB48</f>
-        <v>0.88754583573853807</v>
+        <v>0.88754889097705958</v>
       </c>
       <c r="AG48" s="6">
         <f>SUM(AG10:AG47)</f>
@@ -9145,15 +9145,15 @@
       </c>
       <c r="AI48" s="7">
         <f>AJ48-AH48</f>
-        <v>2880848</v>
+        <v>2880881</v>
       </c>
       <c r="AJ48" s="8">
         <f>SUM(AJ10:AJ47)</f>
-        <v>9363656</v>
+        <v>9363689</v>
       </c>
       <c r="AK48" s="5">
         <f>AJ48/AG48</f>
-        <v>0.89219617907999416</v>
+        <v>0.89219932341527408</v>
       </c>
       <c r="AL48" s="6">
         <f>SUM(AL10:AL47)</f>
@@ -9165,15 +9165,15 @@
       </c>
       <c r="AN48" s="7">
         <f>AO48-AM48</f>
-        <v>1785286</v>
+        <v>1785316</v>
       </c>
       <c r="AO48" s="8">
         <f>SUM(AO10:AO47)</f>
-        <v>9435075</v>
+        <v>9435105</v>
       </c>
       <c r="AP48" s="5">
         <f>AO48/AL48</f>
-        <v>0.90042744912410622</v>
+        <v>0.90043031214570113</v>
       </c>
       <c r="AQ48" s="6">
         <f>SUM(AQ10:AQ47)</f>
@@ -9185,15 +9185,15 @@
       </c>
       <c r="AS48" s="7">
         <f>AT48-AR48</f>
-        <v>2955273</v>
+        <v>2955306</v>
       </c>
       <c r="AT48" s="8">
         <f>SUM(AT10:AT47)</f>
-        <v>9520144</v>
+        <v>9520177</v>
       </c>
       <c r="AU48" s="5">
         <f>AT48/AQ48</f>
-        <v>0.91798063514427986</v>
+        <v>0.91798381717187949</v>
       </c>
       <c r="AV48" s="6">
         <f>SUM(AV10:AV47)</f>
@@ -9205,15 +9205,15 @@
       </c>
       <c r="AX48" s="7">
         <f>AY48-AW48</f>
-        <v>1784542</v>
+        <v>1784577</v>
       </c>
       <c r="AY48" s="8">
         <f>SUM(AY10:AY47)</f>
-        <v>9585388</v>
+        <v>9585423</v>
       </c>
       <c r="AZ48" s="5">
         <f>AY48/AV48</f>
-        <v>0.92543300739650269</v>
+        <v>0.92543638651430771</v>
       </c>
       <c r="BA48" s="6">
         <f>SUM(BA10:BA47)</f>
@@ -9225,15 +9225,15 @@
       </c>
       <c r="BC48" s="7">
         <f>BD48-BB48</f>
-        <v>2313783</v>
+        <v>2313816</v>
       </c>
       <c r="BD48" s="8">
         <f>SUM(BD10:BD47)</f>
-        <v>9653781</v>
+        <v>9653814</v>
       </c>
       <c r="BE48" s="5">
         <f>BD48/BA48</f>
-        <v>0.93073628174086154</v>
+        <v>0.93073946332301027</v>
       </c>
       <c r="BF48" s="6">
         <f>SUM(BF10:BF47)</f>
@@ -9245,15 +9245,15 @@
       </c>
       <c r="BH48" s="7">
         <f>BI48-BG48</f>
-        <v>9066712</v>
+        <v>9066746</v>
       </c>
       <c r="BI48" s="8">
         <f>SUM(BI10:BI47)</f>
-        <v>9676085</v>
+        <v>9676119</v>
       </c>
       <c r="BJ48" s="5">
         <f>BI48/BF48</f>
-        <v>0.92791329706486225</v>
+        <v>0.92791655758315039</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
